--- a/outputs/TRUE-CLOUD-MIGRATION/14_ASSUMPTION_REGISTER.xlsx
+++ b/outputs/TRUE-CLOUD-MIGRATION/14_ASSUMPTION_REGISTER.xlsx
@@ -9,7 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Assumptions'!$A$4:$C$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +28,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00374151"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +67,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,38 +440,80 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>asm_aa507cddcb1f4274b111</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Migration traffic is intended to remain on private network paths (private-path replication), not public internet.</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>True Cloud Migration — Assumption Register</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>asm_7dbd042e3e534603bf82</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Current working register · Generated 2026-08-16T06:30:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Question / statement</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Answer / outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>asm_bed66b2730bf49c086f2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Migration traffic is intended to remain on private network paths (private-path replication), not public internet.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>asm_b1adfdf6543c4e3c9b8a</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Thailand Region is the primary AWS target region for landing zone and legacy zone.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:C6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>